--- a/artfynd/A 34931-2024 artfynd.xlsx
+++ b/artfynd/A 34931-2024 artfynd.xlsx
@@ -975,48 +975,48 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128354576</v>
+        <v>128356285</v>
       </c>
       <c r="B5" t="n">
-        <v>92647</v>
+        <v>86623</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>788</v>
+        <v>3762</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gul taggsvamp</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum geogenium</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Banker</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Skommarbo, Skommarbo, Dlr</t>
+          <t>Långviksgruvorna, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>565080</v>
+        <v>565102</v>
       </c>
       <c r="R5" t="n">
-        <v>6683506</v>
+        <v>6683543</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1060,60 +1060,60 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Patric Engfeldt</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Patric Engfeldt, Philipp Weiss, Janolof Hermansson</t>
+          <t>Philipp Weiss, Janolof Hermansson, Patric Engfeldt</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128356285</v>
+        <v>128354576</v>
       </c>
       <c r="B6" t="n">
-        <v>86623</v>
+        <v>92647</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>3762</v>
+        <v>788</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Gul taggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Hydnellum geogenium</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>(Fr.) Banker</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Långviksgruvorna, Dlr</t>
+          <t>Skommarbo, Skommarbo, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>565102</v>
+        <v>565080</v>
       </c>
       <c r="R6" t="n">
-        <v>6683543</v>
+        <v>6683506</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1157,12 +1157,12 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Patric Engfeldt</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Janolof Hermansson, Patric Engfeldt</t>
+          <t>Patric Engfeldt, Philipp Weiss, Janolof Hermansson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>

--- a/artfynd/A 34931-2024 artfynd.xlsx
+++ b/artfynd/A 34931-2024 artfynd.xlsx
@@ -975,48 +975,48 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128356285</v>
+        <v>128354576</v>
       </c>
       <c r="B5" t="n">
-        <v>86623</v>
+        <v>92647</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>3762</v>
+        <v>788</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Gul taggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Hydnellum geogenium</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>(Fr.) Banker</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Långviksgruvorna, Dlr</t>
+          <t>Skommarbo, Skommarbo, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>565102</v>
+        <v>565080</v>
       </c>
       <c r="R5" t="n">
-        <v>6683543</v>
+        <v>6683506</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1060,60 +1060,60 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Patric Engfeldt</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Janolof Hermansson, Patric Engfeldt</t>
+          <t>Patric Engfeldt, Philipp Weiss, Janolof Hermansson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128354576</v>
+        <v>128356285</v>
       </c>
       <c r="B6" t="n">
-        <v>92647</v>
+        <v>86623</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>788</v>
+        <v>3762</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gul taggsvamp</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum geogenium</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Banker</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Skommarbo, Skommarbo, Dlr</t>
+          <t>Långviksgruvorna, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>565080</v>
+        <v>565102</v>
       </c>
       <c r="R6" t="n">
-        <v>6683506</v>
+        <v>6683543</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1157,12 +1157,12 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Patric Engfeldt</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Patric Engfeldt, Philipp Weiss, Janolof Hermansson</t>
+          <t>Philipp Weiss, Janolof Hermansson, Patric Engfeldt</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>

--- a/artfynd/A 34931-2024 artfynd.xlsx
+++ b/artfynd/A 34931-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128356295</v>
       </c>
       <c r="B2" t="n">
-        <v>90892</v>
+        <v>90895</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>128354540</v>
       </c>
       <c r="B3" t="n">
-        <v>92663</v>
+        <v>92668</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -881,7 +881,7 @@
         <v>128353547</v>
       </c>
       <c r="B4" t="n">
-        <v>92679</v>
+        <v>92684</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -975,48 +975,48 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128356285</v>
+        <v>128354576</v>
       </c>
       <c r="B5" t="n">
-        <v>86623</v>
+        <v>92652</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>3762</v>
+        <v>788</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Gul taggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Hydnellum geogenium</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>(Fr.) Banker</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Långviksgruvorna, Dlr</t>
+          <t>Skommarbo, Skommarbo, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>565102</v>
+        <v>565080</v>
       </c>
       <c r="R5" t="n">
-        <v>6683543</v>
+        <v>6683506</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1060,60 +1060,60 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Patric Engfeldt</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Janolof Hermansson, Patric Engfeldt</t>
+          <t>Patric Engfeldt, Philipp Weiss, Janolof Hermansson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128354576</v>
+        <v>128356285</v>
       </c>
       <c r="B6" t="n">
-        <v>92647</v>
+        <v>86624</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>788</v>
+        <v>3762</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gul taggsvamp</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum geogenium</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Banker</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Skommarbo, Skommarbo, Dlr</t>
+          <t>Långviksgruvorna, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>565080</v>
+        <v>565102</v>
       </c>
       <c r="R6" t="n">
-        <v>6683506</v>
+        <v>6683543</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1157,12 +1157,12 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Patric Engfeldt</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Patric Engfeldt, Philipp Weiss, Janolof Hermansson</t>
+          <t>Philipp Weiss, Janolof Hermansson, Patric Engfeldt</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
@@ -1172,7 +1172,7 @@
         <v>128356340</v>
       </c>
       <c r="B7" t="n">
-        <v>92663</v>
+        <v>92668</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1269,7 +1269,7 @@
         <v>128353419</v>
       </c>
       <c r="B8" t="n">
-        <v>103918</v>
+        <v>103923</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1366,7 +1366,7 @@
         <v>128356246</v>
       </c>
       <c r="B9" t="n">
-        <v>92290</v>
+        <v>92295</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1472,7 +1472,7 @@
         <v>128356341</v>
       </c>
       <c r="B10" t="n">
-        <v>92663</v>
+        <v>92668</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1569,7 +1569,7 @@
         <v>128354598</v>
       </c>
       <c r="B11" t="n">
-        <v>92663</v>
+        <v>92668</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 34931-2024 artfynd.xlsx
+++ b/artfynd/A 34931-2024 artfynd.xlsx
@@ -975,48 +975,48 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128354576</v>
+        <v>128356285</v>
       </c>
       <c r="B5" t="n">
-        <v>92652</v>
+        <v>86624</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>788</v>
+        <v>3762</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gul taggsvamp</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum geogenium</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Banker</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Skommarbo, Skommarbo, Dlr</t>
+          <t>Långviksgruvorna, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>565080</v>
+        <v>565102</v>
       </c>
       <c r="R5" t="n">
-        <v>6683506</v>
+        <v>6683543</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1060,60 +1060,60 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Patric Engfeldt</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Patric Engfeldt, Philipp Weiss, Janolof Hermansson</t>
+          <t>Philipp Weiss, Janolof Hermansson, Patric Engfeldt</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128356285</v>
+        <v>128354576</v>
       </c>
       <c r="B6" t="n">
-        <v>86624</v>
+        <v>92652</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>3762</v>
+        <v>788</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Gul taggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Hydnellum geogenium</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>(Fr.) Banker</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Långviksgruvorna, Dlr</t>
+          <t>Skommarbo, Skommarbo, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>565102</v>
+        <v>565080</v>
       </c>
       <c r="R6" t="n">
-        <v>6683543</v>
+        <v>6683506</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1157,60 +1157,60 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Patric Engfeldt</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Janolof Hermansson, Patric Engfeldt</t>
+          <t>Patric Engfeldt, Philipp Weiss, Janolof Hermansson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128356340</v>
+        <v>128353419</v>
       </c>
       <c r="B7" t="n">
-        <v>92668</v>
+        <v>103923</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4368</v>
+        <v>222412</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Långviksgruvorna, Dlr</t>
+          <t>Skommarbo, Skommarbo, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>565086</v>
+        <v>565085</v>
       </c>
       <c r="R7" t="n">
-        <v>6683525</v>
+        <v>6683411</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1254,60 +1254,60 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Patric Engfeldt</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Janolof Hermansson, Patric Engfeldt</t>
+          <t>Patric Engfeldt, Philipp Weiss, Janolof Hermansson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128353419</v>
+        <v>128356340</v>
       </c>
       <c r="B8" t="n">
-        <v>103923</v>
+        <v>92668</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>222412</v>
+        <v>4368</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Scop.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Skommarbo, Skommarbo, Dlr</t>
+          <t>Långviksgruvorna, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>565085</v>
+        <v>565086</v>
       </c>
       <c r="R8" t="n">
-        <v>6683411</v>
+        <v>6683525</v>
       </c>
       <c r="S8" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1351,12 +1351,12 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Patric Engfeldt</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Patric Engfeldt, Philipp Weiss, Janolof Hermansson</t>
+          <t>Philipp Weiss, Janolof Hermansson, Patric Engfeldt</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>

--- a/artfynd/A 34931-2024 artfynd.xlsx
+++ b/artfynd/A 34931-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128356295</v>
       </c>
       <c r="B2" t="n">
-        <v>90895</v>
+        <v>90987</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>128354540</v>
       </c>
       <c r="B3" t="n">
-        <v>92668</v>
+        <v>92760</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -881,7 +881,7 @@
         <v>128353547</v>
       </c>
       <c r="B4" t="n">
-        <v>92684</v>
+        <v>92776</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -978,7 +978,7 @@
         <v>128356285</v>
       </c>
       <c r="B5" t="n">
-        <v>86624</v>
+        <v>86716</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1075,7 +1075,7 @@
         <v>128354576</v>
       </c>
       <c r="B6" t="n">
-        <v>92652</v>
+        <v>92744</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1169,48 +1169,48 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128353419</v>
+        <v>128356340</v>
       </c>
       <c r="B7" t="n">
-        <v>103923</v>
+        <v>92760</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>222412</v>
+        <v>4368</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Scop.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Skommarbo, Skommarbo, Dlr</t>
+          <t>Långviksgruvorna, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>565085</v>
+        <v>565086</v>
       </c>
       <c r="R7" t="n">
-        <v>6683411</v>
+        <v>6683525</v>
       </c>
       <c r="S7" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1254,60 +1254,60 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Patric Engfeldt</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Patric Engfeldt, Philipp Weiss, Janolof Hermansson</t>
+          <t>Philipp Weiss, Janolof Hermansson, Patric Engfeldt</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128356340</v>
+        <v>128353419</v>
       </c>
       <c r="B8" t="n">
-        <v>92668</v>
+        <v>104016</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4368</v>
+        <v>222412</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Långviksgruvorna, Dlr</t>
+          <t>Skommarbo, Skommarbo, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>565086</v>
+        <v>565085</v>
       </c>
       <c r="R8" t="n">
-        <v>6683525</v>
+        <v>6683411</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1351,12 +1351,12 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Patric Engfeldt</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Janolof Hermansson, Patric Engfeldt</t>
+          <t>Patric Engfeldt, Philipp Weiss, Janolof Hermansson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
@@ -1366,7 +1366,7 @@
         <v>128356246</v>
       </c>
       <c r="B9" t="n">
-        <v>92295</v>
+        <v>92387</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1472,7 +1472,7 @@
         <v>128356341</v>
       </c>
       <c r="B10" t="n">
-        <v>92668</v>
+        <v>92760</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1569,7 +1569,7 @@
         <v>128354598</v>
       </c>
       <c r="B11" t="n">
-        <v>92668</v>
+        <v>92760</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 34931-2024 artfynd.xlsx
+++ b/artfynd/A 34931-2024 artfynd.xlsx
@@ -975,48 +975,48 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128356285</v>
+        <v>128354576</v>
       </c>
       <c r="B5" t="n">
-        <v>86716</v>
+        <v>92744</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>3762</v>
+        <v>788</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Gul taggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Hydnellum geogenium</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>(Fr.) Banker</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Långviksgruvorna, Dlr</t>
+          <t>Skommarbo, Skommarbo, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>565102</v>
+        <v>565080</v>
       </c>
       <c r="R5" t="n">
-        <v>6683543</v>
+        <v>6683506</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1060,60 +1060,60 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Patric Engfeldt</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Janolof Hermansson, Patric Engfeldt</t>
+          <t>Patric Engfeldt, Philipp Weiss, Janolof Hermansson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128354576</v>
+        <v>128356285</v>
       </c>
       <c r="B6" t="n">
-        <v>92744</v>
+        <v>86716</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>788</v>
+        <v>3762</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gul taggsvamp</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum geogenium</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Banker</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Skommarbo, Skommarbo, Dlr</t>
+          <t>Långviksgruvorna, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>565080</v>
+        <v>565102</v>
       </c>
       <c r="R6" t="n">
-        <v>6683506</v>
+        <v>6683543</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1157,12 +1157,12 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Patric Engfeldt</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Patric Engfeldt, Philipp Weiss, Janolof Hermansson</t>
+          <t>Philipp Weiss, Janolof Hermansson, Patric Engfeldt</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>

--- a/artfynd/A 34931-2024 artfynd.xlsx
+++ b/artfynd/A 34931-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128356295</v>
       </c>
       <c r="B2" t="n">
-        <v>90987</v>
+        <v>90999</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>128354540</v>
       </c>
       <c r="B3" t="n">
-        <v>92760</v>
+        <v>92772</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -881,7 +881,7 @@
         <v>128353547</v>
       </c>
       <c r="B4" t="n">
-        <v>92776</v>
+        <v>92788</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -975,48 +975,48 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128354576</v>
+        <v>128356285</v>
       </c>
       <c r="B5" t="n">
-        <v>92744</v>
+        <v>86727</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>788</v>
+        <v>3762</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gul taggsvamp</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum geogenium</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Banker</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Skommarbo, Skommarbo, Dlr</t>
+          <t>Långviksgruvorna, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>565080</v>
+        <v>565102</v>
       </c>
       <c r="R5" t="n">
-        <v>6683506</v>
+        <v>6683543</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1060,60 +1060,60 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Patric Engfeldt</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Patric Engfeldt, Philipp Weiss, Janolof Hermansson</t>
+          <t>Philipp Weiss, Janolof Hermansson, Patric Engfeldt</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128356285</v>
+        <v>128354576</v>
       </c>
       <c r="B6" t="n">
-        <v>86716</v>
+        <v>92756</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>3762</v>
+        <v>788</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Gul taggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Hydnellum geogenium</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>(Fr.) Banker</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Långviksgruvorna, Dlr</t>
+          <t>Skommarbo, Skommarbo, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>565102</v>
+        <v>565080</v>
       </c>
       <c r="R6" t="n">
-        <v>6683543</v>
+        <v>6683506</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1157,12 +1157,12 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Patric Engfeldt</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Janolof Hermansson, Patric Engfeldt</t>
+          <t>Patric Engfeldt, Philipp Weiss, Janolof Hermansson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
@@ -1172,7 +1172,7 @@
         <v>128356340</v>
       </c>
       <c r="B7" t="n">
-        <v>92760</v>
+        <v>92772</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1269,7 +1269,7 @@
         <v>128353419</v>
       </c>
       <c r="B8" t="n">
-        <v>104016</v>
+        <v>104036</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1366,7 +1366,7 @@
         <v>128356246</v>
       </c>
       <c r="B9" t="n">
-        <v>92387</v>
+        <v>92399</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1472,7 +1472,7 @@
         <v>128356341</v>
       </c>
       <c r="B10" t="n">
-        <v>92760</v>
+        <v>92772</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1569,7 +1569,7 @@
         <v>128354598</v>
       </c>
       <c r="B11" t="n">
-        <v>92760</v>
+        <v>92772</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 34931-2024 artfynd.xlsx
+++ b/artfynd/A 34931-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128356295</v>
       </c>
       <c r="B2" t="n">
-        <v>90999</v>
+        <v>91001</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>128354540</v>
       </c>
       <c r="B3" t="n">
-        <v>92772</v>
+        <v>92774</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -881,7 +881,7 @@
         <v>128353547</v>
       </c>
       <c r="B4" t="n">
-        <v>92788</v>
+        <v>92790</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -978,7 +978,7 @@
         <v>128356285</v>
       </c>
       <c r="B5" t="n">
-        <v>86727</v>
+        <v>86729</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1075,7 +1075,7 @@
         <v>128354576</v>
       </c>
       <c r="B6" t="n">
-        <v>92756</v>
+        <v>92758</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1172,7 +1172,7 @@
         <v>128356340</v>
       </c>
       <c r="B7" t="n">
-        <v>92772</v>
+        <v>92774</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1269,7 +1269,7 @@
         <v>128353419</v>
       </c>
       <c r="B8" t="n">
-        <v>104036</v>
+        <v>104048</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1366,7 +1366,7 @@
         <v>128356246</v>
       </c>
       <c r="B9" t="n">
-        <v>92399</v>
+        <v>92401</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1472,7 +1472,7 @@
         <v>128356341</v>
       </c>
       <c r="B10" t="n">
-        <v>92772</v>
+        <v>92774</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1569,7 +1569,7 @@
         <v>128354598</v>
       </c>
       <c r="B11" t="n">
-        <v>92772</v>
+        <v>92774</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 34931-2024 artfynd.xlsx
+++ b/artfynd/A 34931-2024 artfynd.xlsx
@@ -975,48 +975,48 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128356285</v>
+        <v>128354576</v>
       </c>
       <c r="B5" t="n">
-        <v>86729</v>
+        <v>92758</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>3762</v>
+        <v>788</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Gul taggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Hydnellum geogenium</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>(Fr.) Banker</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Långviksgruvorna, Dlr</t>
+          <t>Skommarbo, Skommarbo, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>565102</v>
+        <v>565080</v>
       </c>
       <c r="R5" t="n">
-        <v>6683543</v>
+        <v>6683506</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1060,60 +1060,60 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Patric Engfeldt</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Janolof Hermansson, Patric Engfeldt</t>
+          <t>Patric Engfeldt, Philipp Weiss, Janolof Hermansson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128354576</v>
+        <v>128356285</v>
       </c>
       <c r="B6" t="n">
-        <v>92758</v>
+        <v>86729</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>788</v>
+        <v>3762</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gul taggsvamp</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum geogenium</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Banker</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Skommarbo, Skommarbo, Dlr</t>
+          <t>Långviksgruvorna, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>565080</v>
+        <v>565102</v>
       </c>
       <c r="R6" t="n">
-        <v>6683506</v>
+        <v>6683543</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1157,12 +1157,12 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Patric Engfeldt</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Patric Engfeldt, Philipp Weiss, Janolof Hermansson</t>
+          <t>Philipp Weiss, Janolof Hermansson, Patric Engfeldt</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
@@ -1269,7 +1269,7 @@
         <v>128353419</v>
       </c>
       <c r="B8" t="n">
-        <v>104048</v>
+        <v>104057</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 34931-2024 artfynd.xlsx
+++ b/artfynd/A 34931-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128356295</v>
       </c>
       <c r="B2" t="n">
-        <v>91001</v>
+        <v>91002</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>128354540</v>
       </c>
       <c r="B3" t="n">
-        <v>92774</v>
+        <v>92775</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -881,7 +881,7 @@
         <v>128353547</v>
       </c>
       <c r="B4" t="n">
-        <v>92790</v>
+        <v>92791</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -975,48 +975,48 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128354576</v>
+        <v>128356285</v>
       </c>
       <c r="B5" t="n">
-        <v>92758</v>
+        <v>86729</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>788</v>
+        <v>3762</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gul taggsvamp</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum geogenium</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Banker</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Skommarbo, Skommarbo, Dlr</t>
+          <t>Långviksgruvorna, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>565080</v>
+        <v>565102</v>
       </c>
       <c r="R5" t="n">
-        <v>6683506</v>
+        <v>6683543</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1060,60 +1060,60 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Patric Engfeldt</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Patric Engfeldt, Philipp Weiss, Janolof Hermansson</t>
+          <t>Philipp Weiss, Janolof Hermansson, Patric Engfeldt</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128356285</v>
+        <v>128354576</v>
       </c>
       <c r="B6" t="n">
-        <v>86729</v>
+        <v>92759</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>3762</v>
+        <v>788</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Gul taggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Hydnellum geogenium</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>(Fr.) Banker</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Långviksgruvorna, Dlr</t>
+          <t>Skommarbo, Skommarbo, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>565102</v>
+        <v>565080</v>
       </c>
       <c r="R6" t="n">
-        <v>6683543</v>
+        <v>6683506</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1157,12 +1157,12 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Patric Engfeldt</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Janolof Hermansson, Patric Engfeldt</t>
+          <t>Patric Engfeldt, Philipp Weiss, Janolof Hermansson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
@@ -1172,7 +1172,7 @@
         <v>128356340</v>
       </c>
       <c r="B7" t="n">
-        <v>92774</v>
+        <v>92775</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1269,7 +1269,7 @@
         <v>128353419</v>
       </c>
       <c r="B8" t="n">
-        <v>104057</v>
+        <v>104060</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1366,7 +1366,7 @@
         <v>128356246</v>
       </c>
       <c r="B9" t="n">
-        <v>92401</v>
+        <v>92402</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1472,7 +1472,7 @@
         <v>128356341</v>
       </c>
       <c r="B10" t="n">
-        <v>92774</v>
+        <v>92775</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1569,7 +1569,7 @@
         <v>128354598</v>
       </c>
       <c r="B11" t="n">
-        <v>92774</v>
+        <v>92775</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 34931-2024 artfynd.xlsx
+++ b/artfynd/A 34931-2024 artfynd.xlsx
@@ -1169,48 +1169,48 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128356340</v>
+        <v>128353419</v>
       </c>
       <c r="B7" t="n">
-        <v>92775</v>
+        <v>104060</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4368</v>
+        <v>222412</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Långviksgruvorna, Dlr</t>
+          <t>Skommarbo, Skommarbo, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>565086</v>
+        <v>565085</v>
       </c>
       <c r="R7" t="n">
-        <v>6683525</v>
+        <v>6683411</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1254,60 +1254,60 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Patric Engfeldt</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Janolof Hermansson, Patric Engfeldt</t>
+          <t>Patric Engfeldt, Philipp Weiss, Janolof Hermansson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128353419</v>
+        <v>128356340</v>
       </c>
       <c r="B8" t="n">
-        <v>104060</v>
+        <v>92775</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>222412</v>
+        <v>4368</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Scop.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Skommarbo, Skommarbo, Dlr</t>
+          <t>Långviksgruvorna, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>565085</v>
+        <v>565086</v>
       </c>
       <c r="R8" t="n">
-        <v>6683411</v>
+        <v>6683525</v>
       </c>
       <c r="S8" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1351,12 +1351,12 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Patric Engfeldt</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Patric Engfeldt, Philipp Weiss, Janolof Hermansson</t>
+          <t>Philipp Weiss, Janolof Hermansson, Patric Engfeldt</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>

--- a/artfynd/A 34931-2024 artfynd.xlsx
+++ b/artfynd/A 34931-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128356295</v>
       </c>
       <c r="B2" t="n">
-        <v>91002</v>
+        <v>91029</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>128354540</v>
       </c>
       <c r="B3" t="n">
-        <v>92775</v>
+        <v>92802</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -881,7 +881,7 @@
         <v>128353547</v>
       </c>
       <c r="B4" t="n">
-        <v>92791</v>
+        <v>92818</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -975,48 +975,48 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128356285</v>
+        <v>128354576</v>
       </c>
       <c r="B5" t="n">
-        <v>86729</v>
+        <v>92786</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>3762</v>
+        <v>788</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Gul taggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Hydnellum geogenium</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>(Fr.) Banker</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Långviksgruvorna, Dlr</t>
+          <t>Skommarbo, Skommarbo, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>565102</v>
+        <v>565080</v>
       </c>
       <c r="R5" t="n">
-        <v>6683543</v>
+        <v>6683506</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1060,60 +1060,60 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Patric Engfeldt</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Janolof Hermansson, Patric Engfeldt</t>
+          <t>Patric Engfeldt, Philipp Weiss, Janolof Hermansson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128354576</v>
+        <v>128356285</v>
       </c>
       <c r="B6" t="n">
-        <v>92759</v>
+        <v>86756</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>788</v>
+        <v>3762</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gul taggsvamp</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum geogenium</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Banker</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Skommarbo, Skommarbo, Dlr</t>
+          <t>Långviksgruvorna, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>565080</v>
+        <v>565102</v>
       </c>
       <c r="R6" t="n">
-        <v>6683506</v>
+        <v>6683543</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1157,60 +1157,60 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Patric Engfeldt</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Patric Engfeldt, Philipp Weiss, Janolof Hermansson</t>
+          <t>Philipp Weiss, Janolof Hermansson, Patric Engfeldt</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128353419</v>
+        <v>128356340</v>
       </c>
       <c r="B7" t="n">
-        <v>104060</v>
+        <v>92802</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>222412</v>
+        <v>4368</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Scop.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Skommarbo, Skommarbo, Dlr</t>
+          <t>Långviksgruvorna, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>565085</v>
+        <v>565086</v>
       </c>
       <c r="R7" t="n">
-        <v>6683411</v>
+        <v>6683525</v>
       </c>
       <c r="S7" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1254,60 +1254,60 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Patric Engfeldt</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Patric Engfeldt, Philipp Weiss, Janolof Hermansson</t>
+          <t>Philipp Weiss, Janolof Hermansson, Patric Engfeldt</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128356340</v>
+        <v>128353419</v>
       </c>
       <c r="B8" t="n">
-        <v>92775</v>
+        <v>104087</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4368</v>
+        <v>222412</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Långviksgruvorna, Dlr</t>
+          <t>Skommarbo, Skommarbo, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>565086</v>
+        <v>565085</v>
       </c>
       <c r="R8" t="n">
-        <v>6683525</v>
+        <v>6683411</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1351,12 +1351,12 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Patric Engfeldt</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Janolof Hermansson, Patric Engfeldt</t>
+          <t>Patric Engfeldt, Philipp Weiss, Janolof Hermansson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
@@ -1366,7 +1366,7 @@
         <v>128356246</v>
       </c>
       <c r="B9" t="n">
-        <v>92402</v>
+        <v>92429</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1472,7 +1472,7 @@
         <v>128356341</v>
       </c>
       <c r="B10" t="n">
-        <v>92775</v>
+        <v>92802</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1569,7 +1569,7 @@
         <v>128354598</v>
       </c>
       <c r="B11" t="n">
-        <v>92775</v>
+        <v>92802</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 34931-2024 artfynd.xlsx
+++ b/artfynd/A 34931-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:AY20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128356295</v>
+        <v>128354576</v>
       </c>
       <c r="B2" t="n">
-        <v>91043</v>
+        <v>93199</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,46 +686,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5747</v>
+        <v>788</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Läderdoftande fingersvamp</t>
+          <t>Gul taggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Ramaria safraniolens</t>
+          <t>Hydnellum geogenium</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Christan</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Fr.) Banker</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Långviksgruvorna, Dlr</t>
+          <t>Skommarbo, Skommarbo, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>565077</v>
+        <v>565080</v>
       </c>
       <c r="R2" t="n">
-        <v>6683476</v>
+        <v>6683506</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -769,60 +760,60 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Patric Engfeldt</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Janolof Hermansson, Patric Engfeldt</t>
+          <t>Patric Engfeldt, Philipp Weiss, Janolof Hermansson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128354540</v>
+        <v>128356311</v>
       </c>
       <c r="B3" t="n">
-        <v>92816</v>
+        <v>93199</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4368</v>
+        <v>788</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Gul taggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Hydnellum geogenium</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
+          <t>(Fr.) Banker</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Skommarbo, Skommarbo, Dlr</t>
+          <t>Långviksgruvorna, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>565071</v>
+        <v>565121</v>
       </c>
       <c r="R3" t="n">
-        <v>6683539</v>
+        <v>6683581</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -866,22 +857,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Patric Engfeldt</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Patric Engfeldt, Philipp Weiss, Janolof Hermansson</t>
+          <t>Philipp Weiss, Janolof Hermansson, Patric Engfeldt</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128353547</v>
+        <v>128353366</v>
       </c>
       <c r="B4" t="n">
-        <v>92834</v>
+        <v>87146</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -889,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5964</v>
+        <v>3762</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -913,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>565102</v>
+        <v>565080</v>
       </c>
       <c r="R4" t="n">
-        <v>6683449</v>
+        <v>6683389</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -975,48 +966,48 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128354576</v>
+        <v>128356285</v>
       </c>
       <c r="B5" t="n">
-        <v>92800</v>
+        <v>87146</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>788</v>
+        <v>3762</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gul taggsvamp</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum geogenium</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Banker</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Skommarbo, Skommarbo, Dlr</t>
+          <t>Långviksgruvorna, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>565080</v>
+        <v>565102</v>
       </c>
       <c r="R5" t="n">
-        <v>6683506</v>
+        <v>6683543</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1060,60 +1051,60 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Patric Engfeldt</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Patric Engfeldt, Philipp Weiss, Janolof Hermansson</t>
+          <t>Philipp Weiss, Janolof Hermansson, Patric Engfeldt</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128356285</v>
+        <v>128354540</v>
       </c>
       <c r="B6" t="n">
-        <v>86764</v>
+        <v>93215</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>3762</v>
+        <v>4368</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>(Scop.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Långviksgruvorna, Dlr</t>
+          <t>Skommarbo, Skommarbo, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>565102</v>
+        <v>565071</v>
       </c>
       <c r="R6" t="n">
-        <v>6683543</v>
+        <v>6683539</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1157,22 +1148,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Patric Engfeldt</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Janolof Hermansson, Patric Engfeldt</t>
+          <t>Patric Engfeldt, Philipp Weiss, Janolof Hermansson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128356340</v>
+        <v>128354598</v>
       </c>
       <c r="B7" t="n">
-        <v>92816</v>
+        <v>93215</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1200,17 +1191,17 @@
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Långviksgruvorna, Dlr</t>
+          <t>Skommarbo, Skommarbo, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>565086</v>
+        <v>565072</v>
       </c>
       <c r="R7" t="n">
-        <v>6683525</v>
+        <v>6683512</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1254,60 +1245,60 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Patric Engfeldt</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Janolof Hermansson, Patric Engfeldt</t>
+          <t>Patric Engfeldt, Philipp Weiss, Janolof Hermansson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128353419</v>
+        <v>128356340</v>
       </c>
       <c r="B8" t="n">
-        <v>104104</v>
+        <v>93215</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>222412</v>
+        <v>4368</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Scop.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Skommarbo, Skommarbo, Dlr</t>
+          <t>Långviksgruvorna, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>565085</v>
+        <v>565086</v>
       </c>
       <c r="R8" t="n">
-        <v>6683411</v>
+        <v>6683525</v>
       </c>
       <c r="S8" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1351,66 +1342,57 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Patric Engfeldt</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Patric Engfeldt, Philipp Weiss, Janolof Hermansson</t>
+          <t>Philipp Weiss, Janolof Hermansson, Patric Engfeldt</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128356246</v>
+        <v>128356341</v>
       </c>
       <c r="B9" t="n">
-        <v>92443</v>
+        <v>93215</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4769</v>
+        <v>4368</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Scop.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Långviksgruvorna, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>565122</v>
+        <v>565093</v>
       </c>
       <c r="R9" t="n">
-        <v>6683547</v>
+        <v>6683532</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1469,10 +1451,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128356341</v>
+        <v>128356352</v>
       </c>
       <c r="B10" t="n">
-        <v>92816</v>
+        <v>93215</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1504,10 +1486,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>565093</v>
+        <v>565124</v>
       </c>
       <c r="R10" t="n">
-        <v>6683532</v>
+        <v>6683563</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1566,10 +1548,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128354598</v>
+        <v>128356353</v>
       </c>
       <c r="B11" t="n">
-        <v>92816</v>
+        <v>93215</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1597,17 +1579,17 @@
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Skommarbo, Skommarbo, Dlr</t>
+          <t>Långviksgruvorna, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>565072</v>
+        <v>565118</v>
       </c>
       <c r="R11" t="n">
-        <v>6683512</v>
+        <v>6683561</v>
       </c>
       <c r="S11" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1651,15 +1633,956 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Philipp Weiss, Janolof Hermansson, Patric Engfeldt</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>128356238</v>
+      </c>
+      <c r="B12" t="n">
+        <v>92869</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>4769</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Svavelriska</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Lactarius scrobiculatus</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Långviksgruvorna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>565080</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6683376</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Garpenberg</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Philipp Weiss, Janolof Hermansson, Patric Engfeldt</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>128356241</v>
+      </c>
+      <c r="B13" t="n">
+        <v>92869</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>4769</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Svavelriska</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Lactarius scrobiculatus</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Långviksgruvorna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>565075</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6683397</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Garpenberg</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Philipp Weiss, Janolof Hermansson, Patric Engfeldt</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>128356246</v>
+      </c>
+      <c r="B14" t="n">
+        <v>92869</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>4769</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Svavelriska</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Lactarius scrobiculatus</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Långviksgruvorna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>565122</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6683547</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Garpenberg</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Philipp Weiss, Janolof Hermansson, Patric Engfeldt</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>128356295</v>
+      </c>
+      <c r="B15" t="n">
+        <v>91435</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>5747</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Läderdoftande fingersvamp</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Ramaria safraniolens</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Christan</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Långviksgruvorna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>565077</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6683476</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Garpenberg</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Philipp Weiss, Janolof Hermansson, Patric Engfeldt</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>128353547</v>
+      </c>
+      <c r="B16" t="n">
+        <v>93233</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>5964</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Fjällig taggsvamp s.str.</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Sarcodon imbricatus</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Skommarbo, Skommarbo, Dlr</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>565102</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6683449</v>
+      </c>
+      <c r="S16" t="n">
+        <v>25</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Garpenberg</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
           <t>Patric Engfeldt</t>
         </is>
       </c>
-      <c r="AX11" t="inlineStr">
+      <c r="AX16" t="inlineStr">
         <is>
           <t>Patric Engfeldt, Philipp Weiss, Janolof Hermansson</t>
         </is>
       </c>
-      <c r="AY11" t="inlineStr"/>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>128356314</v>
+      </c>
+      <c r="B17" t="n">
+        <v>93233</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>5964</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Fjällig taggsvamp s.str.</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Sarcodon imbricatus</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Långviksgruvorna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>565093</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6683369</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Garpenberg</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Philipp Weiss, Janolof Hermansson, Patric Engfeldt</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>128356322</v>
+      </c>
+      <c r="B18" t="n">
+        <v>93233</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>5964</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Fjällig taggsvamp s.str.</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Sarcodon imbricatus</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Långviksgruvorna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>565121</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6683569</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Garpenberg</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Philipp Weiss, Janolof Hermansson, Patric Engfeldt</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>128356218</v>
+      </c>
+      <c r="B19" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Långviksgruvorna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>565169</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6683577</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Garpenberg</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Philipp Weiss, Janolof Hermansson, Patric Engfeldt</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>128353419</v>
+      </c>
+      <c r="B20" t="n">
+        <v>104628</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>222412</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Tibast</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Daphne mezereum</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Skommarbo, Skommarbo, Dlr</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>565085</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6683411</v>
+      </c>
+      <c r="S20" t="n">
+        <v>25</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Garpenberg</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Patric Engfeldt</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Patric Engfeldt, Philipp Weiss, Janolof Hermansson</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 34931-2024 artfynd.xlsx
+++ b/artfynd/A 34931-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY20"/>
+  <dimension ref="A1:AZ20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128354576</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128356311</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128353366</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128356285</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128354540</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1254,6 +1284,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128354598</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1351,6 +1386,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128356340</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1448,6 +1488,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128356341</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1545,6 +1590,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128356352</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1642,6 +1692,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128356353</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1748,6 +1803,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128356238</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1854,6 +1914,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128356241</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1960,6 +2025,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128356246</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2066,6 +2136,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128356295</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2163,6 +2238,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128353547</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2269,6 +2349,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128356314</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2375,6 +2460,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128356322</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2486,6 +2576,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128356218</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2583,8 +2678,34 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128353419</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>